--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/88.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/88.xlsx
@@ -426,13 +426,13 @@
         <v>-8.075898198142694</v>
       </c>
       <c r="E2">
-        <v>-3.588589079969648</v>
+        <v>-8.072931790515444</v>
       </c>
       <c r="F2">
-        <v>-0.8081230790899963</v>
+        <v>-1.201319263972421</v>
       </c>
       <c r="G2">
-        <v>-11.67327423900635</v>
+        <v>-13.32660657366658</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.911064076428598</v>
       </c>
       <c r="E3">
-        <v>-4.446102622206997</v>
+        <v>-8.964875454635623</v>
       </c>
       <c r="F3">
-        <v>-1.067791408845557</v>
+        <v>-1.142114188959535</v>
       </c>
       <c r="G3">
-        <v>-11.69705028999762</v>
+        <v>-12.5802194971409</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.592643051735448</v>
       </c>
       <c r="E4">
-        <v>-6.431736343762223</v>
+        <v>-10.27385552751581</v>
       </c>
       <c r="F4">
-        <v>-1.120265998710698</v>
+        <v>-1.37821546610545</v>
       </c>
       <c r="G4">
-        <v>-10.85542325078814</v>
+        <v>-12.08733310966774</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.107551306733752</v>
       </c>
       <c r="E5">
-        <v>-6.612048013429654</v>
+        <v>-10.56999610782138</v>
       </c>
       <c r="F5">
-        <v>-0.6085743419600121</v>
+        <v>-1.303607727604909</v>
       </c>
       <c r="G5">
-        <v>-10.60566375873469</v>
+        <v>-12.13742546613743</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.432108187756922</v>
       </c>
       <c r="E6">
-        <v>-7.541370579473289</v>
+        <v>-10.89776754557685</v>
       </c>
       <c r="F6">
-        <v>-0.5749442821411578</v>
+        <v>-1.284429365495295</v>
       </c>
       <c r="G6">
-        <v>-10.05265845018967</v>
+        <v>-10.86538976826471</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.566407343382744</v>
       </c>
       <c r="E7">
-        <v>-8.64771547181509</v>
+        <v>-12.45790476690339</v>
       </c>
       <c r="F7">
-        <v>-0.6192619381909313</v>
+        <v>-1.315512195550541</v>
       </c>
       <c r="G7">
-        <v>-10.0751513202144</v>
+        <v>-10.59739291987005</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.514168893263856</v>
       </c>
       <c r="E8">
-        <v>-9.833631739929281</v>
+        <v>-13.06567740575615</v>
       </c>
       <c r="F8">
-        <v>-0.7074068567880212</v>
+        <v>-1.405438932431053</v>
       </c>
       <c r="G8">
-        <v>-9.120101787616299</v>
+        <v>-9.75407672891011</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.295237315097747</v>
       </c>
       <c r="E9">
-        <v>-10.63587019264449</v>
+        <v>-14.47885739756496</v>
       </c>
       <c r="F9">
-        <v>-0.5751803668509556</v>
+        <v>-1.412203380642313</v>
       </c>
       <c r="G9">
-        <v>-8.541803585472568</v>
+        <v>-8.888596621743918</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.947637982846895</v>
       </c>
       <c r="E10">
-        <v>-12.02343733021308</v>
+        <v>-14.85932478060985</v>
       </c>
       <c r="F10">
-        <v>-0.2241373139947896</v>
+        <v>-1.493598761641393</v>
       </c>
       <c r="G10">
-        <v>-7.586918529783701</v>
+        <v>-8.00890231565141</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.5285400086077073</v>
       </c>
       <c r="E11">
-        <v>-12.37548013495085</v>
+        <v>-16.15816271143481</v>
       </c>
       <c r="F11">
-        <v>-0.1609850683075637</v>
+        <v>-1.375421382855807</v>
       </c>
       <c r="G11">
-        <v>-5.942381793650941</v>
+        <v>-7.599653741899152</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.9002757371977463</v>
       </c>
       <c r="E12">
-        <v>-12.96760762674298</v>
+        <v>-16.77716563370991</v>
       </c>
       <c r="F12">
-        <v>-0.3524704771386974</v>
+        <v>-1.76151266052442</v>
       </c>
       <c r="G12">
-        <v>-5.720024676825822</v>
+        <v>-6.644619873768592</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.270592930869708</v>
       </c>
       <c r="E13">
-        <v>-13.7111528970157</v>
+        <v>-17.87080169939773</v>
       </c>
       <c r="F13">
-        <v>-0.3351741657682437</v>
+        <v>-1.495565305855639</v>
       </c>
       <c r="G13">
-        <v>-5.634791698159747</v>
+        <v>-5.769020520567245</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.507548161916803</v>
       </c>
       <c r="E14">
-        <v>-15.75709955343009</v>
+        <v>-19.48998097291804</v>
       </c>
       <c r="F14">
-        <v>-0.4067757589640246</v>
+        <v>-1.550374235061868</v>
       </c>
       <c r="G14">
-        <v>-4.924118302268208</v>
+        <v>-4.605704059702258</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.549866930065609</v>
       </c>
       <c r="E15">
-        <v>-16.50158344946223</v>
+        <v>-20.64486444601311</v>
       </c>
       <c r="F15">
-        <v>0.02751324766907503</v>
+        <v>-1.680097398707673</v>
       </c>
       <c r="G15">
-        <v>-4.300419251685017</v>
+        <v>-4.016103944223598</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.36046703942954</v>
       </c>
       <c r="E16">
-        <v>-17.26463220011636</v>
+        <v>-21.82969257276019</v>
       </c>
       <c r="F16">
-        <v>0.3474950080224681</v>
+        <v>-1.707942968952779</v>
       </c>
       <c r="G16">
-        <v>-2.644523165836322</v>
+        <v>-3.819507044278994</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.92831254373788</v>
       </c>
       <c r="E17">
-        <v>-17.83943664747262</v>
+        <v>-22.2637073094161</v>
       </c>
       <c r="F17">
-        <v>0.2671077501525956</v>
+        <v>-1.499278876922389</v>
       </c>
       <c r="G17">
-        <v>-3.028809105180652</v>
+        <v>-3.04967678669742</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.266411325002109</v>
       </c>
       <c r="E18">
-        <v>-18.73899314795121</v>
+        <v>-23.28043420779075</v>
       </c>
       <c r="F18">
-        <v>0.1812209610955373</v>
+        <v>-1.422352538061413</v>
       </c>
       <c r="G18">
-        <v>-2.535480196499294</v>
+        <v>-2.667187039631777</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.413635013062951</v>
       </c>
       <c r="E19">
-        <v>-20.05881725560053</v>
+        <v>-24.21476969990346</v>
       </c>
       <c r="F19">
-        <v>0.3718730323194547</v>
+        <v>-1.102307821785407</v>
       </c>
       <c r="G19">
-        <v>-2.619976945190675</v>
+        <v>-2.358448216520493</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.418542070238596</v>
       </c>
       <c r="E20">
-        <v>-21.44909644016423</v>
+        <v>-25.19309185315742</v>
       </c>
       <c r="F20">
-        <v>0.6555424792037287</v>
+        <v>-1.094430047784784</v>
       </c>
       <c r="G20">
-        <v>-1.398051878999786</v>
+        <v>-1.960403653180997</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.325325043426306</v>
       </c>
       <c r="E21">
-        <v>-21.75411243307096</v>
+        <v>-26.12720307185858</v>
       </c>
       <c r="F21">
-        <v>1.457355736539093</v>
+        <v>-1.019293810881257</v>
       </c>
       <c r="G21">
-        <v>-1.498463726718595</v>
+        <v>-1.818185952324692</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.170855317241393</v>
       </c>
       <c r="E22">
-        <v>-22.42679145850814</v>
+        <v>-26.54938115623872</v>
       </c>
       <c r="F22">
-        <v>1.275587077342798</v>
+        <v>-0.8098046649176792</v>
       </c>
       <c r="G22">
-        <v>-1.117347231307877</v>
+        <v>-1.937841598424596</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.984939405696491</v>
       </c>
       <c r="E23">
-        <v>-21.77171374266559</v>
+        <v>-27.08134522877939</v>
       </c>
       <c r="F23">
-        <v>0.801081661671185</v>
+        <v>-0.7431368279729722</v>
       </c>
       <c r="G23">
-        <v>-1.690447440970701</v>
+        <v>-1.828735971217381</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.783881163322466</v>
       </c>
       <c r="E24">
-        <v>-23.85067842911236</v>
+        <v>-27.8125928403193</v>
       </c>
       <c r="F24">
-        <v>1.347671608734411</v>
+        <v>-0.430142346662193</v>
       </c>
       <c r="G24">
-        <v>-1.394798891239259</v>
+        <v>-2.283433692184035</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.575901372972021</v>
       </c>
       <c r="E25">
-        <v>-23.13607273535104</v>
+        <v>-27.94768019187067</v>
       </c>
       <c r="F25">
-        <v>1.256309311144848</v>
+        <v>-0.697289177330228</v>
       </c>
       <c r="G25">
-        <v>-1.934486791625015</v>
+        <v>-2.364309338127542</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.365695202450879</v>
       </c>
       <c r="E26">
-        <v>-22.9796461840127</v>
+        <v>-27.97499586275407</v>
       </c>
       <c r="F26">
-        <v>1.312863610468775</v>
+        <v>-0.6558293888201128</v>
       </c>
       <c r="G26">
-        <v>-1.637603359701977</v>
+        <v>-2.138341561532914</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.156018464292039</v>
       </c>
       <c r="E27">
-        <v>-23.58881014865927</v>
+        <v>-28.23119708635443</v>
       </c>
       <c r="F27">
-        <v>1.054668117955392</v>
+        <v>-0.4490788254901897</v>
       </c>
       <c r="G27">
-        <v>-1.697154443825271</v>
+        <v>-2.71128251577568</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.952298571969934</v>
       </c>
       <c r="E28">
-        <v>-22.73380514606212</v>
+        <v>-28.20503600821934</v>
       </c>
       <c r="F28">
-        <v>0.9004956904159592</v>
+        <v>-0.5577854797595688</v>
       </c>
       <c r="G28">
-        <v>-1.950971032973305</v>
+        <v>-2.760923213431108</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.764432137146713</v>
       </c>
       <c r="E29">
-        <v>-22.49465077834452</v>
+        <v>-28.37490858122181</v>
       </c>
       <c r="F29">
-        <v>1.171786014832797</v>
+        <v>-0.6856323912380333</v>
       </c>
       <c r="G29">
-        <v>-1.785201805160567</v>
+        <v>-2.825335503983055</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.608157940942145</v>
       </c>
       <c r="E30">
-        <v>-23.12848481826058</v>
+        <v>-27.6241574893005</v>
       </c>
       <c r="F30">
-        <v>1.265964761591879</v>
+        <v>-0.5790944028291833</v>
       </c>
       <c r="G30">
-        <v>-2.316433503815707</v>
+        <v>-3.195405939028773</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.496087380085428</v>
       </c>
       <c r="E31">
-        <v>-22.47160045549172</v>
+        <v>-27.70997529490544</v>
       </c>
       <c r="F31">
-        <v>0.9335922816274107</v>
+        <v>-0.3357043209060354</v>
       </c>
       <c r="G31">
-        <v>-2.391761317503099</v>
+        <v>-2.793510527417384</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.44385073239944</v>
       </c>
       <c r="E32">
-        <v>-22.84591693256454</v>
+        <v>-27.17932779035474</v>
       </c>
       <c r="F32">
-        <v>1.510813598511357</v>
+        <v>-0.6338693689718978</v>
       </c>
       <c r="G32">
-        <v>-2.401851845347752</v>
+        <v>-3.326718559727997</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.461579565902729</v>
       </c>
       <c r="E33">
-        <v>-22.0032760400814</v>
+        <v>-26.73074774158266</v>
       </c>
       <c r="F33">
-        <v>1.159590789928783</v>
+        <v>-0.7805765494773015</v>
       </c>
       <c r="G33">
-        <v>-2.858471074333465</v>
+        <v>-3.018415730963429</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.551629391652262</v>
       </c>
       <c r="E34">
-        <v>-20.98515781591293</v>
+        <v>-27.22630061043855</v>
       </c>
       <c r="F34">
-        <v>0.6397463411997448</v>
+        <v>-0.5408230004524434</v>
       </c>
       <c r="G34">
-        <v>-2.656174918946461</v>
+        <v>-2.899934919929526</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.704631671418244</v>
       </c>
       <c r="E35">
-        <v>-21.00442456324881</v>
+        <v>-25.64680942433831</v>
       </c>
       <c r="F35">
-        <v>0.9405936429158721</v>
+        <v>-0.5432211240835479</v>
       </c>
       <c r="G35">
-        <v>-2.188700213950898</v>
+        <v>-2.991720867519296</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.902793708726716</v>
       </c>
       <c r="E36">
-        <v>-20.7951774702813</v>
+        <v>-25.52076776705242</v>
       </c>
       <c r="F36">
-        <v>1.060894127354833</v>
+        <v>-0.4746157357836929</v>
       </c>
       <c r="G36">
-        <v>-2.27284451212248</v>
+        <v>-3.243242612171741</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.121914748072691</v>
       </c>
       <c r="E37">
-        <v>-19.03446090802217</v>
+        <v>-25.05601926659278</v>
       </c>
       <c r="F37">
-        <v>1.419549048275324</v>
+        <v>-0.4364627899455533</v>
       </c>
       <c r="G37">
-        <v>-2.176711674788506</v>
+        <v>-3.248832216341315</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.332364888935627</v>
       </c>
       <c r="E38">
-        <v>-19.23672229954132</v>
+        <v>-24.69007566355081</v>
       </c>
       <c r="F38">
-        <v>1.07868248896255</v>
+        <v>-0.5454171260683695</v>
       </c>
       <c r="G38">
-        <v>-2.20188447413602</v>
+        <v>-2.789777162652092</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.505843847092443</v>
       </c>
       <c r="E39">
-        <v>-18.5363372013562</v>
+        <v>-24.04067123437797</v>
       </c>
       <c r="F39">
-        <v>0.696989013835399</v>
+        <v>-0.3814774184825277</v>
       </c>
       <c r="G39">
-        <v>-2.799977341769572</v>
+        <v>-2.704933184930093</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.615318587084807</v>
       </c>
       <c r="E40">
-        <v>-17.87551559425141</v>
+        <v>-22.98798167914163</v>
       </c>
       <c r="F40">
-        <v>1.5779063879337</v>
+        <v>-0.1737203887582033</v>
       </c>
       <c r="G40">
-        <v>-2.76284994293935</v>
+        <v>-2.798102827153153</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.637823973229929</v>
       </c>
       <c r="E41">
-        <v>-16.53491712355531</v>
+        <v>-22.27271977799098</v>
       </c>
       <c r="F41">
-        <v>1.484988416361679</v>
+        <v>-0.2492111669101278</v>
       </c>
       <c r="G41">
-        <v>-2.474704673162768</v>
+        <v>-2.953643157657909</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.554891941645479</v>
       </c>
       <c r="E42">
-        <v>-16.73122696324598</v>
+        <v>-21.90168018465345</v>
       </c>
       <c r="F42">
-        <v>1.272321653040962</v>
+        <v>-0.1758194717568972</v>
       </c>
       <c r="G42">
-        <v>-2.576085107124879</v>
+        <v>-2.992412714835941</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.360965837492133</v>
       </c>
       <c r="E43">
-        <v>-16.677986947273</v>
+        <v>-21.05032585481082</v>
       </c>
       <c r="F43">
-        <v>1.640988222391688</v>
+        <v>-0.2751937388663371</v>
       </c>
       <c r="G43">
-        <v>-3.132964760643116</v>
+        <v>-3.144509473225019</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.06107036826403</v>
       </c>
       <c r="E44">
-        <v>-15.26975343015206</v>
+        <v>-19.40012624590537</v>
       </c>
       <c r="F44">
-        <v>1.318468344316117</v>
+        <v>-0.3458775009798161</v>
       </c>
       <c r="G44">
-        <v>-2.800282798886732</v>
+        <v>-3.671858994673174</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.669066221931506</v>
       </c>
       <c r="E45">
-        <v>-14.53459349354416</v>
+        <v>-19.60320997326684</v>
       </c>
       <c r="F45">
-        <v>1.272414430190076</v>
+        <v>0.2013403485747317</v>
       </c>
       <c r="G45">
-        <v>-3.151759510954541</v>
+        <v>-3.51625339555364</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.20848394452214</v>
       </c>
       <c r="E46">
-        <v>-14.64059175297643</v>
+        <v>-19.10446743811348</v>
       </c>
       <c r="F46">
-        <v>1.329341494845263</v>
+        <v>-0.06161162956552658</v>
       </c>
       <c r="G46">
-        <v>-3.075617144954721</v>
+        <v>-3.714529004270329</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.709606951152518</v>
       </c>
       <c r="E47">
-        <v>-12.85395915205037</v>
+        <v>-17.62586606151597</v>
       </c>
       <c r="F47">
-        <v>1.024896593498778</v>
+        <v>-0.1767315042673795</v>
       </c>
       <c r="G47">
-        <v>-3.410766260349707</v>
+        <v>-4.790226265912963</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.203143957080165</v>
       </c>
       <c r="E48">
-        <v>-12.18112230458284</v>
+        <v>-16.51723690294551</v>
       </c>
       <c r="F48">
-        <v>1.295539134606627</v>
+        <v>0.13049008461329</v>
       </c>
       <c r="G48">
-        <v>-3.945613840263539</v>
+        <v>-4.507759365622052</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.713566982517462</v>
       </c>
       <c r="E49">
-        <v>-12.26703978725957</v>
+        <v>-16.44276982389134</v>
       </c>
       <c r="F49">
-        <v>1.546521203776432</v>
+        <v>0.01605029954913547</v>
       </c>
       <c r="G49">
-        <v>-3.614292076439126</v>
+        <v>-4.883612599937085</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.262601602744652</v>
       </c>
       <c r="E50">
-        <v>-10.72199948909878</v>
+        <v>-15.80195423573824</v>
       </c>
       <c r="F50">
-        <v>1.293158406690981</v>
+        <v>0.04292419483075703</v>
       </c>
       <c r="G50">
-        <v>-4.255391739722087</v>
+        <v>-5.16210072547114</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.863427423791287</v>
       </c>
       <c r="E51">
-        <v>-10.67902205830946</v>
+        <v>-14.86148445049877</v>
       </c>
       <c r="F51">
-        <v>1.14374743498284</v>
+        <v>-0.00298641173459997</v>
       </c>
       <c r="G51">
-        <v>-4.10114111704534</v>
+        <v>-5.248628633454407</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.519332972739402</v>
       </c>
       <c r="E52">
-        <v>-10.12532007769464</v>
+        <v>-13.82575661031302</v>
       </c>
       <c r="F52">
-        <v>1.131086667598452</v>
+        <v>-0.1379738502251962</v>
       </c>
       <c r="G52">
-        <v>-4.839556284962049</v>
+        <v>-5.2271552591925</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.225987116583892</v>
       </c>
       <c r="E53">
-        <v>-10.73430130104292</v>
+        <v>-14.04501294257337</v>
       </c>
       <c r="F53">
-        <v>1.224244865717284</v>
+        <v>0.06989335236370053</v>
       </c>
       <c r="G53">
-        <v>-4.880025436868896</v>
+        <v>-5.705973649436451</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.977516336119569</v>
       </c>
       <c r="E54">
-        <v>-8.68853738592683</v>
+        <v>-12.10790118892612</v>
       </c>
       <c r="F54">
-        <v>1.283615614210731</v>
+        <v>-0.1161124060979145</v>
       </c>
       <c r="G54">
-        <v>-4.521228196967606</v>
+        <v>-5.914901096084882</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.7628336958895742</v>
       </c>
       <c r="E55">
-        <v>-8.070659983920763</v>
+        <v>-12.9826671710068</v>
       </c>
       <c r="F55">
-        <v>1.11103023604187</v>
+        <v>0.07116323959219217</v>
       </c>
       <c r="G55">
-        <v>-4.80768953648292</v>
+        <v>-6.451774613801418</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.5666713412564488</v>
       </c>
       <c r="E56">
-        <v>-7.368692512220893</v>
+        <v>-10.96167716144331</v>
       </c>
       <c r="F56">
-        <v>0.9410260507001335</v>
+        <v>0.01471165782621147</v>
       </c>
       <c r="G56">
-        <v>-5.125712167360202</v>
+        <v>-6.714039572446294</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.3748271484730291</v>
       </c>
       <c r="E57">
-        <v>-7.868103714397551</v>
+        <v>-10.76972819364371</v>
       </c>
       <c r="F57">
-        <v>1.115843050652136</v>
+        <v>0.08998291861639414</v>
       </c>
       <c r="G57">
-        <v>-5.700010708790348</v>
+        <v>-6.710133898537989</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.1747070185197082</v>
       </c>
       <c r="E58">
-        <v>-6.647807162936428</v>
+        <v>-10.28839176715271</v>
       </c>
       <c r="F58">
-        <v>1.088634494939783</v>
+        <v>0.1495135420185806</v>
       </c>
       <c r="G58">
-        <v>-6.534524774361345</v>
+        <v>-7.365224542084726</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.04546744466949783</v>
       </c>
       <c r="E59">
-        <v>-5.80359220336118</v>
+        <v>-10.36839092369156</v>
       </c>
       <c r="F59">
-        <v>1.018842884519119</v>
+        <v>0.1710320420411034</v>
       </c>
       <c r="G59">
-        <v>-6.020845111592259</v>
+        <v>-7.094477274263323</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.2911474136276326</v>
       </c>
       <c r="E60">
-        <v>-5.542508879848484</v>
+        <v>-9.318151763136862</v>
       </c>
       <c r="F60">
-        <v>1.062598907469795</v>
+        <v>-0.07124388572527923</v>
       </c>
       <c r="G60">
-        <v>-6.088037845133742</v>
+        <v>-7.401962939970872</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.5601144140783652</v>
       </c>
       <c r="E61">
-        <v>-6.028617346151715</v>
+        <v>-8.882230702482859</v>
       </c>
       <c r="F61">
-        <v>0.9789917855052404</v>
+        <v>-0.1892034038839288</v>
       </c>
       <c r="G61">
-        <v>-6.433653435594501</v>
+        <v>-7.887561433917943</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.848239144363054</v>
       </c>
       <c r="E62">
-        <v>-5.485751093883376</v>
+        <v>-8.260453435042777</v>
       </c>
       <c r="F62">
-        <v>1.219190167825402</v>
+        <v>-0.2196575030804498</v>
       </c>
       <c r="G62">
-        <v>-6.340238383379877</v>
+        <v>-7.933094124959254</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.150165033536078</v>
       </c>
       <c r="E63">
-        <v>-4.3897144720498</v>
+        <v>-6.817636127219992</v>
       </c>
       <c r="F63">
-        <v>1.085095709395024</v>
+        <v>0.1167159914395398</v>
       </c>
       <c r="G63">
-        <v>-6.06512072911295</v>
+        <v>-8.340034800492969</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.45976947963249</v>
       </c>
       <c r="E64">
-        <v>-4.242827847124588</v>
+        <v>-7.413763161517932</v>
       </c>
       <c r="F64">
-        <v>0.7780596748125811</v>
+        <v>-0.1009176628283631</v>
       </c>
       <c r="G64">
-        <v>-6.737575434935181</v>
+        <v>-8.561170088849446</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.77077941509665</v>
       </c>
       <c r="E65">
-        <v>-3.412247880328753</v>
+        <v>-6.801426143419186</v>
       </c>
       <c r="F65">
-        <v>0.978658781809315</v>
+        <v>0.01052260387025437</v>
       </c>
       <c r="G65">
-        <v>-7.439226097519832</v>
+        <v>-8.302066741904408</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.080686726073084</v>
       </c>
       <c r="E66">
-        <v>-4.042680440169776</v>
+        <v>-7.274634735347501</v>
       </c>
       <c r="F66">
-        <v>0.6114824454162257</v>
+        <v>-0.06084787482014543</v>
       </c>
       <c r="G66">
-        <v>-7.128711968086591</v>
+        <v>-8.363241709163376</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.386841195419767</v>
       </c>
       <c r="E67">
-        <v>-3.254454922464542</v>
+        <v>-7.026559269704167</v>
       </c>
       <c r="F67">
-        <v>1.153691157286045</v>
+        <v>-0.4417593711190533</v>
       </c>
       <c r="G67">
-        <v>-6.628080806783889</v>
+        <v>-8.30901393326136</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.68473045103867</v>
       </c>
       <c r="E68">
-        <v>-4.312207242305849</v>
+        <v>-6.658011603161532</v>
       </c>
       <c r="F68">
-        <v>1.09043867914308</v>
+        <v>-0.2691325745800531</v>
       </c>
       <c r="G68">
-        <v>-6.409164651329858</v>
+        <v>-8.623893227650942</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.970775889614891</v>
       </c>
       <c r="E69">
-        <v>-3.250251872603815</v>
+        <v>-6.228312053072122</v>
       </c>
       <c r="F69">
-        <v>0.3585023540708679</v>
+        <v>-0.1932110453786728</v>
       </c>
       <c r="G69">
-        <v>-7.544969085693693</v>
+        <v>-8.156452462335064</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.245875992452254</v>
       </c>
       <c r="E70">
-        <v>-3.731409711007851</v>
+        <v>-6.600111684082097</v>
       </c>
       <c r="F70">
-        <v>0.3847657425766262</v>
+        <v>-0.06788154243731603</v>
       </c>
       <c r="G70">
-        <v>-7.115545983113607</v>
+        <v>-8.060078131126414</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.509762467490835</v>
       </c>
       <c r="E71">
-        <v>-2.945995917369526</v>
+        <v>-6.521400023053947</v>
       </c>
       <c r="F71">
-        <v>0.916915589074251</v>
+        <v>-0.4614695451012648</v>
       </c>
       <c r="G71">
-        <v>-6.63973517063862</v>
+        <v>-8.503210253554435</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.760493949147822</v>
       </c>
       <c r="E72">
-        <v>-4.409654039620301</v>
+        <v>-6.467358437295277</v>
       </c>
       <c r="F72">
-        <v>0.6191199928700372</v>
+        <v>-0.3503573118941559</v>
       </c>
       <c r="G72">
-        <v>-6.386571267638364</v>
+        <v>-8.178389243761893</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.997576077376157</v>
       </c>
       <c r="E73">
-        <v>-3.553835007603483</v>
+        <v>-5.841693764055157</v>
       </c>
       <c r="F73">
-        <v>0.5504019466034014</v>
+        <v>-0.229519217010778</v>
       </c>
       <c r="G73">
-        <v>-7.172577698706476</v>
+        <v>-8.29245659106452</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.219018267540102</v>
       </c>
       <c r="E74">
-        <v>-4.576638054146358</v>
+        <v>-5.844119239468857</v>
       </c>
       <c r="F74">
-        <v>0.3589927475733252</v>
+        <v>-0.369502539307658</v>
       </c>
       <c r="G74">
-        <v>-7.159161082252745</v>
+        <v>-8.013271396724639</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.420938389194143</v>
       </c>
       <c r="E75">
-        <v>-4.462532726208019</v>
+        <v>-6.205045763230432</v>
       </c>
       <c r="F75">
-        <v>0.1866683051363468</v>
+        <v>-0.4486348205622892</v>
       </c>
       <c r="G75">
-        <v>-6.119606968729483</v>
+        <v>-7.732769081738541</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.597629774933505</v>
       </c>
       <c r="E76">
-        <v>-6.488577193953827</v>
+        <v>-7.213561762815897</v>
       </c>
       <c r="F76">
-        <v>0.04620121627623187</v>
+        <v>-0.4742181194303491</v>
       </c>
       <c r="G76">
-        <v>-6.161391935910252</v>
+        <v>-7.775432564474219</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.747053237383357</v>
       </c>
       <c r="E77">
-        <v>-4.255333166423648</v>
+        <v>-7.119632735493575</v>
       </c>
       <c r="F77">
-        <v>0.3534244618917069</v>
+        <v>-0.07913325686954173</v>
       </c>
       <c r="G77">
-        <v>-5.442194458928729</v>
+        <v>-7.111997981214284</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.866602059597421</v>
       </c>
       <c r="E78">
-        <v>-6.166470736445424</v>
+        <v>-8.273374075474319</v>
       </c>
       <c r="F78">
-        <v>-0.01728403310691944</v>
+        <v>-0.661806887998714</v>
       </c>
       <c r="G78">
-        <v>-6.099937618980036</v>
+        <v>-6.854458470279322</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.957395294697915</v>
       </c>
       <c r="E79">
-        <v>-7.388075549473867</v>
+        <v>-7.650529432723758</v>
       </c>
       <c r="F79">
-        <v>0.1555639375286282</v>
+        <v>-0.4259648898498751</v>
       </c>
       <c r="G79">
-        <v>-5.720646034038507</v>
+        <v>-6.764364285184594</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.022861748426982</v>
       </c>
       <c r="E80">
-        <v>-7.074869423834572</v>
+        <v>-9.133632890397379</v>
       </c>
       <c r="F80">
-        <v>0.4987018802598786</v>
+        <v>-0.3413968616980736</v>
       </c>
       <c r="G80">
-        <v>-5.33678564606253</v>
+        <v>-6.466828167113778</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.066043655881413</v>
       </c>
       <c r="E81">
-        <v>-7.494667718125592</v>
+        <v>-9.576473201118548</v>
       </c>
       <c r="F81">
-        <v>0.2245611436100074</v>
+        <v>-0.4918764273558262</v>
       </c>
       <c r="G81">
-        <v>-5.144702723515961</v>
+        <v>-6.170500823788646</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.087273680890871</v>
       </c>
       <c r="E82">
-        <v>-8.113379915607949</v>
+        <v>-9.756996684563546</v>
       </c>
       <c r="F82">
-        <v>0.1879390207322413</v>
+        <v>-0.7518297154979502</v>
       </c>
       <c r="G82">
-        <v>-4.761951901991206</v>
+        <v>-5.760895883399701</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.084922355239873</v>
       </c>
       <c r="E83">
-        <v>-9.337767380224028</v>
+        <v>-10.44702367370453</v>
       </c>
       <c r="F83">
-        <v>0.2813921176464703</v>
+        <v>-0.567576782460659</v>
       </c>
       <c r="G83">
-        <v>-5.327175495222641</v>
+        <v>-5.833905355890184</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.058516551628146</v>
       </c>
       <c r="E84">
-        <v>-10.04869748196288</v>
+        <v>-11.88172560659861</v>
       </c>
       <c r="F84">
-        <v>0.05919995756096172</v>
+        <v>-0.7178956448422685</v>
       </c>
       <c r="G84">
-        <v>-3.989137563341989</v>
+        <v>-5.646456504992841</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.005657758862368</v>
       </c>
       <c r="E85">
-        <v>-12.14375586229336</v>
+        <v>-12.49722737172687</v>
       </c>
       <c r="F85">
-        <v>0.2654195373856902</v>
+        <v>-0.6723702291192133</v>
       </c>
       <c r="G85">
-        <v>-4.336254331942638</v>
+        <v>-4.930527680239391</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.927457812742176</v>
       </c>
       <c r="E86">
-        <v>-12.14439545683739</v>
+        <v>-13.48504376606939</v>
       </c>
       <c r="F86">
-        <v>-0.1434021418157414</v>
+        <v>-0.2483836278747311</v>
       </c>
       <c r="G86">
-        <v>-4.159183190794971</v>
+        <v>-4.7368939754057</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.828805108471727</v>
       </c>
       <c r="E87">
-        <v>-13.74135920298118</v>
+        <v>-15.24509581451655</v>
       </c>
       <c r="F87">
-        <v>0.03602223763063155</v>
+        <v>-0.7493504118613713</v>
       </c>
       <c r="G87">
-        <v>-3.887430786305989</v>
+        <v>-4.588227735409346</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.72119065615537</v>
       </c>
       <c r="E88">
-        <v>-15.89023904887012</v>
+        <v>-15.92532122493095</v>
       </c>
       <c r="F88">
-        <v>0.02758697236792418</v>
+        <v>-0.7971273301852356</v>
       </c>
       <c r="G88">
-        <v>-3.338761924526803</v>
+        <v>-4.594373428176826</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.615465880409909</v>
       </c>
       <c r="E89">
-        <v>-17.36911869062639</v>
+        <v>-17.75246009590807</v>
       </c>
       <c r="F89">
-        <v>-0.1786524882744715</v>
+        <v>-0.7133578482097328</v>
       </c>
       <c r="G89">
-        <v>-3.731261266354774</v>
+        <v>-4.48880535989057</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.523190218625012</v>
       </c>
       <c r="E90">
-        <v>-19.75230610661686</v>
+        <v>-19.22346109578114</v>
       </c>
       <c r="F90">
-        <v>0.1122916811411876</v>
+        <v>-0.5741150863709555</v>
       </c>
       <c r="G90">
-        <v>-3.267611302185192</v>
+        <v>-3.884955800433613</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.45606546002838</v>
       </c>
       <c r="E91">
-        <v>-19.68098300853558</v>
+        <v>-20.64225622930111</v>
       </c>
       <c r="F91">
-        <v>0.2337891564771939</v>
+        <v>-1.019499245997152</v>
       </c>
       <c r="G91">
-        <v>-3.110444477800173</v>
+        <v>-4.413581975986823</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.421753760749041</v>
       </c>
       <c r="E92">
-        <v>-22.20930024106085</v>
+        <v>-22.8911246378353</v>
       </c>
       <c r="F92">
-        <v>0.1577864472703393</v>
+        <v>-1.094560101467023</v>
       </c>
       <c r="G92">
-        <v>-3.784697986645681</v>
+        <v>-4.265730288302895</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.424191548211629</v>
       </c>
       <c r="E93">
-        <v>-23.80624737435934</v>
+        <v>-23.94342379120711</v>
       </c>
       <c r="F93">
-        <v>0.2349936026808644</v>
+        <v>-0.7366763905985388</v>
       </c>
       <c r="G93">
-        <v>-3.319820972518276</v>
+        <v>-4.443926660369333</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.461836259210232</v>
       </c>
       <c r="E94">
-        <v>-26.15501297488963</v>
+        <v>-26.59610893685437</v>
       </c>
       <c r="F94">
-        <v>0.4687274057895785</v>
+        <v>-0.8292514180658005</v>
       </c>
       <c r="G94">
-        <v>-3.575063028213058</v>
+        <v>-3.979892916744857</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.532370942063118</v>
       </c>
       <c r="E95">
-        <v>-27.80938656117653</v>
+        <v>-28.95971811465959</v>
       </c>
       <c r="F95">
-        <v>0.2125887495373462</v>
+        <v>-0.9149791605815213</v>
       </c>
       <c r="G95">
-        <v>-3.483642584866044</v>
+        <v>-4.204255085415951</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.624362222750479</v>
       </c>
       <c r="E96">
-        <v>-31.5865993583457</v>
+        <v>-30.88678947992907</v>
       </c>
       <c r="F96">
-        <v>0.02276421734882546</v>
+        <v>-0.9677030890349042</v>
       </c>
       <c r="G96">
-        <v>-3.270517060915102</v>
+        <v>-4.346015905968811</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.725226319193693</v>
       </c>
       <c r="E97">
-        <v>-31.9747460291302</v>
+        <v>-33.703071696267</v>
       </c>
       <c r="F97">
-        <v>-0.3934257899005077</v>
+        <v>-1.023978228544089</v>
       </c>
       <c r="G97">
-        <v>-4.026854990449803</v>
+        <v>-4.883683090041045</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.817681638632683</v>
       </c>
       <c r="E98">
-        <v>-36.76935854490863</v>
+        <v>-35.24597724380683</v>
       </c>
       <c r="F98">
-        <v>-0.133582674622956</v>
+        <v>-1.320872561014057</v>
       </c>
       <c r="G98">
-        <v>-3.807907506060678</v>
+        <v>-4.795071807874069</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.887699985005774</v>
       </c>
       <c r="E99">
-        <v>-39.52020899342955</v>
+        <v>-38.20954064014582</v>
       </c>
       <c r="F99">
-        <v>0.008001881863535473</v>
+        <v>-1.146545126197109</v>
       </c>
       <c r="G99">
-        <v>-4.505908347706953</v>
+        <v>-4.734839319412495</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.921508707568768</v>
       </c>
       <c r="E100">
-        <v>-40.97691879313388</v>
+        <v>-41.16284560451248</v>
       </c>
       <c r="F100">
-        <v>-0.2328070072324892</v>
+        <v>-1.269838502062385</v>
       </c>
       <c r="G100">
-        <v>-4.070744217771008</v>
+        <v>-4.599213748648751</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.917929279247665</v>
       </c>
       <c r="E101">
-        <v>-42.92423083379492</v>
+        <v>-42.80337653745373</v>
       </c>
       <c r="F101">
-        <v>-0.3456430730048239</v>
+        <v>-1.186317530307722</v>
       </c>
       <c r="G101">
-        <v>-4.342133728761826</v>
+        <v>-4.827345832509412</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.876454145644536</v>
       </c>
       <c r="E102">
-        <v>-45.77120528182332</v>
+        <v>-45.23966899004912</v>
       </c>
       <c r="F102">
-        <v>-0.3725799242090582</v>
+        <v>-1.39541900032679</v>
       </c>
       <c r="G102">
-        <v>-4.326124642929119</v>
+        <v>-4.906331299368953</v>
       </c>
     </row>
   </sheetData>
